--- a/output/details/2026-05-09/preprocessed_data.xlsx
+++ b/output/details/2026-05-09/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46151</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.107978078770294</v>
+        <v>-0.1075103170261057</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2041149764595494</v>
+        <v>-0.1321931741771385</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2038195922719566</v>
+        <v>-0.1319301399023779</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1339405292096876</v>
+        <v>0.0160033235837301</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703768749232771</v>
+        <v>0.001704134560505582</v>
       </c>
       <c r="G2" t="n">
-        <v>1.771032460795426</v>
+        <v>2.354591948309428</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4634138016202604</v>
+        <v>-0.2565322486990882</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
